--- a/Data/Species_qaqc3_CalIPCcategories_lmr_abr2.xlsx
+++ b/Data/Species_qaqc3_CalIPCcategories_lmr_abr2.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/aryan_nps_gov/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bbecker\Projects\PINN_Grazing\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11B00D79-FE00-45A9-873C-99C69B27C947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2818E186-598E-452E-BB86-330AF601EBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E5C11A6B-4D86-6A43-BA48-4868E951628A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5C11A6B-4D86-6A43-BA48-4868E951628A}"/>
   </bookViews>
   <sheets>
     <sheet name="species" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$A$1:$I$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$A$1:$H$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="132">
   <si>
     <t>Species</t>
   </si>
@@ -143,9 +143,6 @@
     <t>G</t>
   </si>
   <si>
-    <t>AG*</t>
-  </si>
-  <si>
     <t>Dead Annual Grass</t>
   </si>
   <si>
@@ -158,18 +155,12 @@
     <t>Amsinkia sp.</t>
   </si>
   <si>
-    <t>AMSIN*</t>
-  </si>
-  <si>
     <t>BRDI</t>
   </si>
   <si>
     <t>Bromus diandrus</t>
   </si>
   <si>
-    <t>BRDI*</t>
-  </si>
-  <si>
     <t>Dead Bromus hordeaceus</t>
   </si>
   <si>
@@ -179,9 +170,6 @@
     <t>Bromus hordeaceus</t>
   </si>
   <si>
-    <t>BRHO*</t>
-  </si>
-  <si>
     <t>BRMA</t>
   </si>
   <si>
@@ -203,9 +191,6 @@
     <t>P</t>
   </si>
   <si>
-    <t>BRNI*</t>
-  </si>
-  <si>
     <t>Dead Brassica nigra</t>
   </si>
   <si>
@@ -278,9 +263,6 @@
     <t>Erodium cicutarium</t>
   </si>
   <si>
-    <t>ERCI*</t>
-  </si>
-  <si>
     <t>Dead Erodium cicutarium</t>
   </si>
   <si>
@@ -308,9 +290,6 @@
     <t>Festuca bromoides</t>
   </si>
   <si>
-    <t>FEMY*</t>
-  </si>
-  <si>
     <t>Dead Festuca myuros</t>
   </si>
   <si>
@@ -332,9 +311,6 @@
     <t>Hirschfeldia incana</t>
   </si>
   <si>
-    <t>HIIN*</t>
-  </si>
-  <si>
     <t>Dead Hirschfeldia incana</t>
   </si>
   <si>
@@ -350,9 +326,6 @@
     <t>Hordeum murinum</t>
   </si>
   <si>
-    <t>HOMU*</t>
-  </si>
-  <si>
     <t>Dead Hordeum murinum</t>
   </si>
   <si>
@@ -425,18 +398,9 @@
     <t>Species2</t>
   </si>
   <si>
-    <t>ACAM*</t>
-  </si>
-  <si>
     <t>AVEN</t>
   </si>
   <si>
-    <t>CRSE*</t>
-  </si>
-  <si>
-    <t>DELO*</t>
-  </si>
-  <si>
     <t>BG</t>
   </si>
   <si>
@@ -479,9 +443,6 @@
     <t>Not listed</t>
   </si>
   <si>
-    <t>lmr notes</t>
-  </si>
-  <si>
     <t>lmr suggested groups</t>
   </si>
   <si>
@@ -500,44 +461,59 @@
     <t>Native Grass</t>
   </si>
   <si>
-    <t>only perennial forb so I'd lump it in with non-native forbs</t>
-  </si>
-  <si>
     <t>Dead Bromus diandrus</t>
   </si>
   <si>
-    <t>Acts as short-lived perennial at PINN</t>
-  </si>
-  <si>
-    <t>This is a huge ag weed but is not considered as big of a problem in natural areas/widl lands. So, you can make the call on what you think it’s role is for this setting</t>
-  </si>
-  <si>
-    <t>Can also be perennial due to mild winters</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Maybe this was Elymus??  No other perennial grasses ever listed </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ABR Replies: no, these were either one of a couple stipa or melica or poa species. One plot had a stipa and at least one had some other species</t>
-    </r>
+    <t>BRNI_d</t>
+  </si>
+  <si>
+    <t>ERCI_d</t>
+  </si>
+  <si>
+    <t>AG_d</t>
+  </si>
+  <si>
+    <t>BRDI_d</t>
+  </si>
+  <si>
+    <t>BRHO_d</t>
+  </si>
+  <si>
+    <t>FEMY_d</t>
+  </si>
+  <si>
+    <t>HOMU_d</t>
+  </si>
+  <si>
+    <t>HIIN_d</t>
+  </si>
+  <si>
+    <t>ACAM_d</t>
+  </si>
+  <si>
+    <t>AMSIN_d</t>
+  </si>
+  <si>
+    <t>CRSE_d</t>
+  </si>
+  <si>
+    <t>DELO_d</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -580,30 +556,7 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -665,20 +618,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -993,21 +945,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C067F225-CDA5-A24E-AC47-0F3CD5128250}">
-  <dimension ref="A1:I58"/>
-  <sheetFormatPr defaultColWidth="10.69921875" defaultRowHeight="15.6"/>
+  <dimension ref="A1:H58"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="22.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.09765625" customWidth="1"/>
-    <col min="9" max="9" width="126.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1019,27 +970,24 @@
         <v>3</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="9" t="s">
+        <v>120</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>7</v>
@@ -1052,286 +1000,283 @@
         <v>NAF</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" si="0"/>
+        <v>NAF</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>NAF</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>NAF</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>NAF</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="str">
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="str">
         <f t="shared" si="0"/>
         <v>NAF</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="str">
+      <c r="G7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="str">
         <f t="shared" si="0"/>
         <v>NAF</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="str">
+      <c r="G8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="str">
         <f t="shared" si="0"/>
         <v>NAF</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="str">
+      <c r="G9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="str">
         <f t="shared" si="0"/>
         <v>NAF</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="G10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="str">
         <f t="shared" si="0"/>
         <v>NAF</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="str">
+      <c r="G11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="str">
         <f t="shared" si="0"/>
         <v>NAF</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="str">
-        <f t="shared" si="0"/>
-        <v>NAF</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="str">
-        <f t="shared" si="0"/>
-        <v>NAF</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="str">
-        <f t="shared" si="0"/>
-        <v>NAF</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="str">
-        <f t="shared" si="0"/>
-        <v>NAF</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1339,7 +1284,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>7</v>
@@ -1352,21 +1297,21 @@
         <v>NAG</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>7</v>
@@ -1379,21 +1324,21 @@
         <v>NAG</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>7</v>
@@ -1406,22 +1351,21 @@
         <v>NAG</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>7</v>
@@ -1434,22 +1378,21 @@
         <v>NAG</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>7</v>
@@ -1462,22 +1405,21 @@
         <v>NAG</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
@@ -1490,21 +1432,21 @@
         <v>NAG</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>7</v>
@@ -1517,21 +1459,21 @@
         <v>NAG</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>7</v>
@@ -1544,22 +1486,21 @@
         <v>NAG</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>7</v>
@@ -1572,21 +1513,21 @@
         <v>NAG</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -1599,21 +1540,21 @@
         <v>NAG</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>7</v>
@@ -1626,22 +1567,21 @@
         <v>NAG</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>7</v>
@@ -1654,22 +1594,21 @@
         <v>NAG</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
@@ -1682,22 +1621,21 @@
         <v>NAG</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>7</v>
@@ -1710,165 +1648,153 @@
         <v>NAG</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v>NAF</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v>NPF</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v>NPF</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="str">
-        <f t="shared" si="0"/>
-        <v>NAF</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="str">
+      <c r="B30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="str">
         <f t="shared" si="0"/>
         <v>NPF</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="str">
+      <c r="G30" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="str">
         <f t="shared" si="0"/>
         <v>NPF</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="str">
-        <f t="shared" si="0"/>
-        <v>NPF</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="str">
-        <f t="shared" si="0"/>
-        <v>NPF</v>
-      </c>
       <c r="G31" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>11</v>
@@ -1883,13 +1809,19 @@
         <f t="shared" si="0"/>
         <v>XXX</v>
       </c>
+      <c r="G32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
@@ -1904,13 +1836,19 @@
         <f t="shared" si="0"/>
         <v>XXX</v>
       </c>
+      <c r="G33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>11</v>
@@ -1925,6 +1863,12 @@
         <f t="shared" ref="F34:F55" si="1">_xlfn.CONCAT(C34:E34)</f>
         <v>XXX</v>
       </c>
+      <c r="G34" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2" t="s">
@@ -1946,17 +1890,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
-      <c r="G35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H35" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
@@ -1971,16 +1917,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G36" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H36" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>6</v>
@@ -1995,17 +1944,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
-      <c r="G37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H37" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="2" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>6</v>
@@ -2020,17 +1971,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
-      <c r="G38" s="2"/>
+      <c r="G38" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H38" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>6</v>
@@ -2045,16 +1998,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G39" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H39" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>6</v>
@@ -2069,16 +2025,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G40" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H40" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
@@ -2093,16 +2052,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G41" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H41" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>6</v>
@@ -2117,16 +2079,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G42" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H42" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6</v>
@@ -2141,16 +2106,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G43" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H43" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -2165,16 +2133,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G44" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H44" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
@@ -2189,16 +2160,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G45" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H45" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>6</v>
@@ -2213,16 +2187,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G46" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H46" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6</v>
@@ -2237,16 +2214,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G47" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H47" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6</v>
@@ -2261,16 +2241,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G48" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H48" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -2285,16 +2268,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G49" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H49" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>6</v>
@@ -2309,16 +2295,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G50" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H50" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>6</v>
@@ -2333,16 +2322,19 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G51" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H51" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6</v>
@@ -2357,22 +2349,25 @@
         <f t="shared" si="1"/>
         <v>YAF</v>
       </c>
+      <c r="G52" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H52" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
@@ -2381,49 +2376,52 @@
         <f t="shared" si="1"/>
         <v>YPG</v>
       </c>
+      <c r="G53" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H53" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="9" t="str">
+      <c r="F54" s="7" t="str">
         <f t="shared" si="1"/>
         <v>YPF</v>
       </c>
+      <c r="G54" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="H54" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I54" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>12</v>
@@ -2432,28 +2430,28 @@
         <f t="shared" si="1"/>
         <v>YPG</v>
       </c>
-      <c r="H55" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="G55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:8">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:8">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2461,12 +2459,7 @@
       <c r="E58" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I55" xr:uid="{C067F225-CDA5-A24E-AC47-0F3CD5128250}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I55">
-      <sortCondition ref="D1:D55"/>
-    </sortState>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I58">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H58">
     <sortCondition ref="C2:C58"/>
     <sortCondition ref="D2:D58"/>
     <sortCondition ref="E2:E58"/>
